--- a/data/trans_bre/P3A_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R2-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 1,07</t>
+          <t>-5,32; 1,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,08</t>
+          <t>-1,41; 4,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,78</t>
+          <t>-1,94; 4,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,82</t>
+          <t>-2,14; 3,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-84,27; 49,58</t>
+          <t>-86,24; 50,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,69; 370,36</t>
+          <t>-44,01; 335,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-65,33; 323,51</t>
+          <t>-58,94; 352,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 118,81</t>
+          <t>-34,02; 126,83</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,16</t>
+          <t>-2,83; 1,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,86</t>
+          <t>-0,06; 4,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,15</t>
+          <t>-0,66; 2,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,42</t>
+          <t>-1,14; 3,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,98; 95,57</t>
+          <t>-56,47; 86,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 350,57</t>
+          <t>-10,81; 355,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,76; 438,78</t>
+          <t>-41,16; 417,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 164,97</t>
+          <t>-26,91; 166,02</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 3,12</t>
+          <t>-3,23; 3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,81</t>
+          <t>-4,42; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,42</t>
+          <t>-2,8; 1,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 5,98</t>
+          <t>-0,8; 6,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 129,56</t>
+          <t>-56,75; 124,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,26; 75,2</t>
+          <t>-57,01; 68,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-84,45; 128,03</t>
+          <t>-77,6; 126,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 115,12</t>
+          <t>-12,23; 117,5</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,77</t>
+          <t>-1,19; 4,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,24</t>
+          <t>-2,08; 2,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,99</t>
+          <t>-0,14; 4,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 0,69</t>
+          <t>-7,21; 0,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 202,57</t>
+          <t>-27,82; 219,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 186,12</t>
+          <t>-49,83; 152,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 833,2</t>
+          <t>-33,6; 882,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,63; 13,68</t>
+          <t>-64,49; 15,42</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 0,35</t>
+          <t>-5,65; 0,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 3,76</t>
+          <t>-5,19; 3,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,97</t>
+          <t>-1,33; 3,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,72</t>
+          <t>-2,6; 2,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 140,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-68,45; 146,44</t>
+          <t>-67,4; 173,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,72; 143,04</t>
+          <t>-53,86; 137,29</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -0,24</t>
+          <t>-5,94; -0,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,39; -0,35</t>
+          <t>-9,57; -0,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 6,65</t>
+          <t>-0,3; 6,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 6,75</t>
+          <t>-0,52; 6,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,55; 10,75</t>
+          <t>-91,93; 29,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,61; 1,78</t>
+          <t>-78,94; -2,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 404,16</t>
+          <t>-15,73; 443,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 142,45</t>
+          <t>-8,58; 129,17</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,51</t>
+          <t>-2,39; 1,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,19</t>
+          <t>-0,26; 4,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,32</t>
+          <t>-1,92; 2,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 2,1</t>
+          <t>-5,27; 2,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-59,62; 70,65</t>
+          <t>-58,92; 73,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 204,09</t>
+          <t>-9,27; 225,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 93,53</t>
+          <t>-40,83; 93,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-62,26; 44,75</t>
+          <t>-61,33; 46,05</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,38</t>
+          <t>-3,72; 0,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,2</t>
+          <t>-0,5; 3,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,68</t>
+          <t>-1,77; 1,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,51</t>
+          <t>0,83; 3,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,36; 16,07</t>
+          <t>-61,19; 16,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 145,35</t>
+          <t>-13,39; 138,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 83,06</t>
+          <t>-47,33; 93,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>34,95; 473,13</t>
+          <t>38,96; 477,42</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,0</t>
+          <t>-1,84; 0,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,78</t>
+          <t>-0,28; 1,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,52</t>
+          <t>-0,18; 1,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,2</t>
+          <t>-0,11; 2,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 1,25</t>
+          <t>-40,49; 1,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 53,72</t>
+          <t>-7,01; 54,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 73,74</t>
+          <t>-10,32; 65,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 60,26</t>
+          <t>-2,14; 61,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,16</t>
+          <t>-5,44; 0,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,79</t>
+          <t>-0,85; 5,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,11</t>
+          <t>-2,41; 3,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 3,7</t>
+          <t>-1,57; 3,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-86,24; 50,85</t>
+          <t>-83,18; 44,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 335,91</t>
+          <t>-34,97; 336,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-58,94; 352,94</t>
+          <t>-69,58; 355,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,02; 126,83</t>
+          <t>-27,26; 131,34</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,97</t>
+          <t>-3,1; 1,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,84</t>
+          <t>-0,05; 4,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,85</t>
+          <t>-0,74; 2,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,48</t>
+          <t>-1,06; 3,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,47; 86,28</t>
+          <t>-58,81; 75,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 355,75</t>
+          <t>-9,37; 371,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 417,4</t>
+          <t>-41,15; 436,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 166,02</t>
+          <t>-24,46; 147,19</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 3,06</t>
+          <t>-3,07; 3,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 2,77</t>
+          <t>-4,41; 3,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,43</t>
+          <t>-2,91; 1,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 6,02</t>
+          <t>-0,5; 5,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,75; 124,32</t>
+          <t>-54,46; 118,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 68,03</t>
+          <t>-57,55; 80,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-77,6; 126,97</t>
+          <t>-82,08; 135,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 117,5</t>
+          <t>-7,77; 121,04</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,76</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-33,97%</t>
+          <t>-19,82%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,81</t>
+          <t>-1,08; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,98</t>
+          <t>-1,99; 3,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,6</t>
+          <t>-0,09; 4,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 0,93</t>
+          <t>-6,31; 1,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 219,17</t>
+          <t>-26,52; 215,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,83; 152,87</t>
+          <t>-49,47; 180,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,6; 882,57</t>
+          <t>-30,39; 800,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,49; 15,42</t>
+          <t>-53,76; 29,28</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,33</t>
+          <t>-5,35; 0,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 3,86</t>
+          <t>-4,53; 3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,05</t>
+          <t>-1,37; 2,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,5</t>
+          <t>-1,7; 3,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-67,4; 173,37</t>
+          <t>-61,71; 146,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,86; 137,29</t>
+          <t>-39,19; 197,82</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,94; -0,29</t>
+          <t>-6,55; -0,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,57; -0,74</t>
+          <t>-9,75; -0,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 6,78</t>
+          <t>-0,55; 6,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 6,37</t>
+          <t>-0,54; 6,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,93; 29,18</t>
+          <t>-92,69; -0,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,94; -2,72</t>
+          <t>-78,79; -2,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 443,18</t>
+          <t>-30,69; 395,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 129,17</t>
+          <t>-8,23; 133,89</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-10,11%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,61</t>
+          <t>-2,39; 1,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,43</t>
+          <t>-0,36; 4,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,46</t>
+          <t>-2,26; 2,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 2,19</t>
+          <t>-1,71; 3,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,92; 73,62</t>
+          <t>-56,39; 84,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 225,11</t>
+          <t>-10,42; 217,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 93,3</t>
+          <t>-46,65; 99,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-61,33; 46,05</t>
+          <t>-22,82; 71,34</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>143,13%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,45</t>
+          <t>-3,85; 0,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,19</t>
+          <t>-0,65; 3,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,83</t>
+          <t>-1,77; 1,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,65</t>
+          <t>0,38; 3,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,19; 16,27</t>
+          <t>-61,44; 7,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 138,74</t>
+          <t>-18,25; 131,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 93,46</t>
+          <t>-46,72; 89,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,96; 477,42</t>
+          <t>12,74; 241,71</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,05</t>
+          <t>-1,9; -0,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,78</t>
+          <t>-0,23; 1,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,43</t>
+          <t>-0,19; 1,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,23</t>
+          <t>0,19; 2,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 1,59</t>
+          <t>-40,95; -0,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 54,19</t>
+          <t>-5,08; 53,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 65,35</t>
+          <t>-7,53; 67,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 61,58</t>
+          <t>3,87; 54,63</t>
         </is>
       </c>
     </row>
